--- a/output/成田赤十字病院_随意契約_X線関連.xlsx
+++ b/output/成田赤十字病院_随意契約_X線関連.xlsx
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">

--- a/output/成田赤十字病院_随意契約_X線関連.xlsx
+++ b/output/成田赤十字病院_随意契約_X線関連.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -759,13 +759,17 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>公表された随意契約に該当なし</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -789,7 +793,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
     </row>
@@ -811,17 +815,13 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>回診用X線装置</t>
+          <t>一般撮影（レントゲン）</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>公表された随意契約に該当なし</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
